--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260930.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>3.97%</t>
         </is>
       </c>
     </row>
@@ -667,44 +667,44 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6,390,000</t>
+          <t>51,253,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>51,253,000</t>
+          <t>6,390,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -770,112 +770,112 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>21,845,000</t>
+          <t>4,063,032,658</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>27,928,000</t>
+          <t>21,845,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>10,592,000</t>
+          <t>27,928,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>33,426,000</t>
+          <t>10,592,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>3,843,058,675</t>
+          <t>3,008,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>36,729,000</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,990,000</t>
+          <t>33,426,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,132 +931,132 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3,008,000</t>
+          <t>36,729,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>10,091,000</t>
+          <t>4,101,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>4,101,000</t>
+          <t>10,091,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>585,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,322,000</t>
+          <t>4,784,400</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -1078,139 +1078,139 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>42,300,500</t>
+          <t>2,322,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>4,409,000</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>4,409,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>4,784,400</t>
+          <t>15,578,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,893,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,578,000</t>
+          <t>9,893,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,788,541,204</t>
+          <t>2,848,931,204</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -1298,95 +1298,95 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>10,015,000</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6,478,000</t>
+          <t>10,015,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>10,287,000</t>
+          <t>6,478,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1569,39 +1569,39 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>50,331,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>50,331,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,593,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
